--- a/research/traditional_assets/database/data/switzerland/switzerland_information_services.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_information_services.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.9437924289494879</v>
+        <v>-0.1052880075542965</v>
       </c>
       <c r="H2">
-        <v>-1.171326659762973</v>
+        <v>-0.2285174693106704</v>
       </c>
       <c r="I2">
-        <v>-2.012426648256817</v>
+        <v>-0.1468366383380548</v>
       </c>
       <c r="J2">
-        <v>-2.012426648256817</v>
+        <v>-0.1468366383380548</v>
       </c>
       <c r="K2">
-        <v>-190.7</v>
+        <v>-74</v>
       </c>
       <c r="L2">
-        <v>-2.194223909791738</v>
+        <v>-0.3493862134088763</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>9.44822373393802e-06</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.0001351351351351351</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,76 +624,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>96.399</v>
+        <v>216.9</v>
       </c>
       <c r="V2">
-        <v>0.07493120870579091</v>
+        <v>0.2049319727891156</v>
       </c>
       <c r="W2">
-        <v>-8.507122437311118</v>
+        <v>0.4164321890827237</v>
       </c>
       <c r="X2">
-        <v>0.07983393011193388</v>
+        <v>0.1660778160744087</v>
       </c>
       <c r="Y2">
-        <v>-8.586956367423051</v>
+        <v>0.2503543730083151</v>
       </c>
       <c r="Z2">
-        <v>1.49227335164835</v>
+        <v>43.22448979591757</v>
       </c>
       <c r="AA2">
-        <v>2.990856107019115</v>
+        <v>-6.346938775510087</v>
       </c>
       <c r="AB2">
-        <v>0.06460788223084432</v>
+        <v>0.1149009815379166</v>
       </c>
       <c r="AC2">
-        <v>2.926248224788271</v>
+        <v>-6.461839757048003</v>
       </c>
       <c r="AD2">
-        <v>839.37</v>
+        <v>776</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>839.37</v>
+        <v>776</v>
       </c>
       <c r="AG2">
-        <v>742.971</v>
+        <v>559.1</v>
       </c>
       <c r="AH2">
-        <v>0.3948359965567039</v>
+        <v>0.4230266027038814</v>
       </c>
       <c r="AI2">
-        <v>1.260656033162116</v>
+        <v>0.9946167649320686</v>
       </c>
       <c r="AJ2">
-        <v>0.3660909665622224</v>
+        <v>0.3456568778979908</v>
       </c>
       <c r="AK2">
-        <v>1.304783279857961</v>
+        <v>0.9925439375110953</v>
       </c>
       <c r="AL2">
-        <v>25.234</v>
+        <v>23.6</v>
       </c>
       <c r="AM2">
-        <v>24.83</v>
+        <v>23.26</v>
       </c>
       <c r="AN2">
-        <v>-9.254355016538037</v>
+        <v>270.3832752613241</v>
       </c>
       <c r="AO2">
-        <v>-6.931124673060157</v>
+        <v>-1.317796610169492</v>
       </c>
       <c r="AP2">
-        <v>-8.191521499448731</v>
+        <v>194.808362369338</v>
       </c>
       <c r="AQ2">
-        <v>-7.043898509867096</v>
+        <v>-1.337059329320722</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Achiko AG (SWX:ACHI)</t>
+          <t>Global Blue Group Holding AG (NYSE:GB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,31 +716,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>-4.314946619217082</v>
+        <v>-0.1052880075542965</v>
       </c>
       <c r="H3">
-        <v>-4.519572953736654</v>
+        <v>-0.2285174693106704</v>
       </c>
       <c r="I3">
-        <v>-4.519572953736654</v>
+        <v>-0.1468366383380548</v>
       </c>
       <c r="J3">
-        <v>-4.519572953736654</v>
+        <v>-0.1468366383380548</v>
       </c>
       <c r="K3">
-        <v>-14.1</v>
+        <v>-74</v>
       </c>
       <c r="L3">
-        <v>-5.01779359430605</v>
+        <v>-0.3493862134088763</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>9.44822373393802e-06</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.0001351351351351351</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,201 +752,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.599</v>
+        <v>216.9</v>
       </c>
       <c r="V3">
-        <v>0.02376984126984127</v>
+        <v>0.2049319727891156</v>
       </c>
       <c r="W3">
-        <v>-20.34632034632035</v>
+        <v>0.4164321890827237</v>
       </c>
       <c r="X3">
-        <v>0.06777493116342123</v>
+        <v>0.1660778160744087</v>
       </c>
       <c r="Y3">
-        <v>-20.41409527748377</v>
+        <v>0.2503543730083151</v>
       </c>
       <c r="Z3">
-        <v>-1.924657534246575</v>
+        <v>43.22448979591757</v>
       </c>
       <c r="AA3">
-        <v>8.698630136986301</v>
+        <v>-6.346938775510087</v>
       </c>
       <c r="AB3">
-        <v>0.06449304089397156</v>
+        <v>0.1149009815379166</v>
       </c>
       <c r="AC3">
-        <v>8.63413709609233</v>
+        <v>-6.461839757048003</v>
       </c>
       <c r="AD3">
-        <v>2.17</v>
+        <v>776</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.17</v>
+        <v>776</v>
       </c>
       <c r="AG3">
-        <v>1.571</v>
+        <v>559.1</v>
       </c>
       <c r="AH3">
-        <v>0.07928388746803069</v>
+        <v>0.4230266027038814</v>
       </c>
       <c r="AI3">
-        <v>-1.154255319148936</v>
+        <v>0.9946167649320686</v>
       </c>
       <c r="AJ3">
-        <v>0.05868290314145904</v>
+        <v>0.3456568778979908</v>
       </c>
       <c r="AK3">
-        <v>-0.6337232755143203</v>
+        <v>0.9925439375110953</v>
       </c>
       <c r="AL3">
-        <v>0.034</v>
+        <v>23.6</v>
       </c>
       <c r="AM3">
-        <v>0.034</v>
+        <v>23.26</v>
       </c>
       <c r="AN3">
-        <v>-0.1708661417322835</v>
+        <v>270.3832752613241</v>
       </c>
       <c r="AO3">
-        <v>-373.5294117647059</v>
+        <v>-1.317796610169492</v>
       </c>
       <c r="AP3">
-        <v>-0.1237007874015748</v>
+        <v>194.808362369338</v>
       </c>
       <c r="AQ3">
-        <v>-373.5294117647059</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Global Blue Group Holding AG (NYSE:GB)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Information Services</t>
-        </is>
-      </c>
-      <c r="G4">
-        <v>-0.83115338882283</v>
-      </c>
-      <c r="H4">
-        <v>-1.059453032104637</v>
-      </c>
-      <c r="I4">
-        <v>-1.928656361474435</v>
-      </c>
-      <c r="J4">
-        <v>-1.928656361474435</v>
-      </c>
-      <c r="K4">
-        <v>-176.6</v>
-      </c>
-      <c r="L4">
-        <v>-2.099881093935791</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>95.8</v>
-      </c>
-      <c r="V4">
-        <v>0.07595338143185602</v>
-      </c>
-      <c r="W4">
-        <v>3.332075471698113</v>
-      </c>
-      <c r="X4">
-        <v>0.09189292906044652</v>
-      </c>
-      <c r="Y4">
-        <v>3.240182542637667</v>
-      </c>
-      <c r="Z4">
-        <v>1.408710217755443</v>
-      </c>
-      <c r="AA4">
-        <v>-2.716917922948071</v>
-      </c>
-      <c r="AB4">
-        <v>0.06472272356771708</v>
-      </c>
-      <c r="AC4">
-        <v>-2.781640646515788</v>
-      </c>
-      <c r="AD4">
-        <v>837.2</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>837.2</v>
-      </c>
-      <c r="AG4">
-        <v>741.4000000000001</v>
-      </c>
-      <c r="AH4">
-        <v>0.3989516321181797</v>
-      </c>
-      <c r="AI4">
-        <v>1.253856522390295</v>
-      </c>
-      <c r="AJ4">
-        <v>0.3702002296899187</v>
-      </c>
-      <c r="AK4">
-        <v>1.296380486098968</v>
-      </c>
-      <c r="AL4">
-        <v>25.2</v>
-      </c>
-      <c r="AM4">
-        <v>24.796</v>
-      </c>
-      <c r="AN4">
-        <v>-10.73333333333333</v>
-      </c>
-      <c r="AO4">
-        <v>-6.436507936507936</v>
-      </c>
-      <c r="AP4">
-        <v>-9.505128205128207</v>
-      </c>
-      <c r="AQ4">
-        <v>-6.541377641555089</v>
+        <v>-1.337059329320722</v>
       </c>
     </row>
   </sheetData>
